--- a/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_freeze_availability_events.xlsx
+++ b/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_freeze_availability_events.xlsx
@@ -760,7 +760,7 @@
     <t>high</t>
   </si>
   <si>
-    <t>NorthBank_D2_v2_20260804</t>
+    <t>NorthBank_D2_v3_20260804</t>
   </si>
 </sst>
 </file>
@@ -1646,10 +1646,10 @@
         <v>1</v>
       </c>
       <c r="M10">
-        <v>1.396825396825397</v>
+        <v>1.527777777777778</v>
       </c>
       <c r="N10">
-        <v>1.396825396825397</v>
+        <v>1.527777777777778</v>
       </c>
       <c r="Q10" t="s">
         <v>242</v>
@@ -1752,10 +1752,10 @@
         <v>1</v>
       </c>
       <c r="M12">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="N12">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="Q12" t="s">
         <v>242</v>
@@ -2282,10 +2282,10 @@
         <v>1</v>
       </c>
       <c r="M22">
-        <v>1.396825396825397</v>
+        <v>1.527777777777778</v>
       </c>
       <c r="N22">
-        <v>1.396825396825397</v>
+        <v>1.527777777777778</v>
       </c>
       <c r="Q22" t="s">
         <v>242</v>
@@ -2388,10 +2388,10 @@
         <v>1</v>
       </c>
       <c r="M24">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="N24">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="Q24" t="s">
         <v>242</v>
@@ -2918,10 +2918,10 @@
         <v>1</v>
       </c>
       <c r="M34">
-        <v>1.396825396825397</v>
+        <v>1.527777777777778</v>
       </c>
       <c r="N34">
-        <v>1.396825396825397</v>
+        <v>1.527777777777778</v>
       </c>
       <c r="Q34" t="s">
         <v>242</v>
@@ -3024,10 +3024,10 @@
         <v>1</v>
       </c>
       <c r="M36">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="N36">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="Q36" t="s">
         <v>242</v>
@@ -3554,10 +3554,10 @@
         <v>0</v>
       </c>
       <c r="M46">
-        <v>1.396825396825397</v>
+        <v>1.527777777777778</v>
       </c>
       <c r="N46">
-        <v>1.396825396825397</v>
+        <v>1.527777777777778</v>
       </c>
       <c r="Q46" t="s">
         <v>242</v>
@@ -3660,10 +3660,10 @@
         <v>0</v>
       </c>
       <c r="M48">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="N48">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="Q48" t="s">
         <v>242</v>
@@ -5568,10 +5568,10 @@
         <v>1</v>
       </c>
       <c r="M84">
-        <v>1.388888888888889</v>
+        <v>1.514550264550265</v>
       </c>
       <c r="N84">
-        <v>1.388888888888889</v>
+        <v>1.514550264550265</v>
       </c>
       <c r="Q84" t="s">
         <v>242</v>
@@ -5674,10 +5674,10 @@
         <v>1</v>
       </c>
       <c r="M86">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="N86">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="Q86" t="s">
         <v>242</v>
@@ -5727,10 +5727,10 @@
         <v>1</v>
       </c>
       <c r="M87">
-        <v>1.552579365079365</v>
+        <v>1.651785714285714</v>
       </c>
       <c r="N87">
-        <v>1.552579365079365</v>
+        <v>1.651785714285714</v>
       </c>
       <c r="O87" t="s">
         <v>235</v>
@@ -5786,10 +5786,10 @@
         <v>1</v>
       </c>
       <c r="M88">
-        <v>1</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="N88">
-        <v>1</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="Q88" t="s">
         <v>242</v>
@@ -6263,10 +6263,10 @@
         <v>1</v>
       </c>
       <c r="M97">
-        <v>1.388888888888889</v>
+        <v>1.514550264550265</v>
       </c>
       <c r="N97">
-        <v>1.388888888888889</v>
+        <v>1.514550264550265</v>
       </c>
       <c r="Q97" t="s">
         <v>242</v>
@@ -6369,10 +6369,10 @@
         <v>1</v>
       </c>
       <c r="M99">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="N99">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="Q99" t="s">
         <v>242</v>
@@ -6422,10 +6422,10 @@
         <v>1</v>
       </c>
       <c r="M100">
-        <v>1.552579365079365</v>
+        <v>1.651785714285714</v>
       </c>
       <c r="N100">
-        <v>1.552579365079365</v>
+        <v>1.651785714285714</v>
       </c>
       <c r="O100" t="s">
         <v>236</v>
@@ -6481,10 +6481,10 @@
         <v>1</v>
       </c>
       <c r="M101">
-        <v>1</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="N101">
-        <v>1</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="Q101" t="s">
         <v>242</v>
@@ -6958,10 +6958,10 @@
         <v>1</v>
       </c>
       <c r="M110">
-        <v>1.388888888888889</v>
+        <v>1.514550264550265</v>
       </c>
       <c r="N110">
-        <v>1.388888888888889</v>
+        <v>1.514550264550265</v>
       </c>
       <c r="Q110" t="s">
         <v>242</v>
@@ -7064,10 +7064,10 @@
         <v>1</v>
       </c>
       <c r="M112">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="N112">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="Q112" t="s">
         <v>242</v>
@@ -7117,10 +7117,10 @@
         <v>1</v>
       </c>
       <c r="M113">
-        <v>1.552579365079365</v>
+        <v>1.651785714285714</v>
       </c>
       <c r="N113">
-        <v>1.552579365079365</v>
+        <v>1.651785714285714</v>
       </c>
       <c r="O113" t="s">
         <v>237</v>
@@ -7176,10 +7176,10 @@
         <v>1</v>
       </c>
       <c r="M114">
-        <v>1</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="N114">
-        <v>1</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="O114" t="s">
         <v>238</v>
@@ -7659,10 +7659,10 @@
         <v>0</v>
       </c>
       <c r="M123">
-        <v>1.391534391534391</v>
+        <v>1.51984126984127</v>
       </c>
       <c r="N123">
-        <v>1.391534391534391</v>
+        <v>1.51984126984127</v>
       </c>
       <c r="Q123" t="s">
         <v>242</v>
@@ -7765,10 +7765,10 @@
         <v>0</v>
       </c>
       <c r="M125">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="N125">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="Q125" t="s">
         <v>242</v>
@@ -7818,10 +7818,10 @@
         <v>0</v>
       </c>
       <c r="M126">
-        <v>1.552579365079365</v>
+        <v>1.651785714285714</v>
       </c>
       <c r="N126">
-        <v>1.552579365079365</v>
+        <v>1.651785714285714</v>
       </c>
       <c r="O126" t="s">
         <v>239</v>
@@ -7877,10 +7877,10 @@
         <v>0</v>
       </c>
       <c r="M127">
-        <v>1</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="N127">
-        <v>1</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="Q127" t="s">
         <v>242</v>
@@ -8354,10 +8354,10 @@
         <v>1</v>
       </c>
       <c r="M136">
-        <v>1.404761904761905</v>
+        <v>1.543650793650794</v>
       </c>
       <c r="N136">
-        <v>1.404761904761905</v>
+        <v>1.543650793650794</v>
       </c>
       <c r="Q136" t="s">
         <v>242</v>
@@ -8460,10 +8460,10 @@
         <v>1</v>
       </c>
       <c r="M138">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="N138">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="Q138" t="s">
         <v>242</v>
@@ -8937,10 +8937,10 @@
         <v>1</v>
       </c>
       <c r="M147">
-        <v>1.396825396825397</v>
+        <v>1.527777777777778</v>
       </c>
       <c r="N147">
-        <v>1.396825396825397</v>
+        <v>1.527777777777778</v>
       </c>
       <c r="Q147" t="s">
         <v>242</v>
@@ -9043,10 +9043,10 @@
         <v>1</v>
       </c>
       <c r="M149">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="N149">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="Q149" t="s">
         <v>242</v>
@@ -9573,10 +9573,10 @@
         <v>1</v>
       </c>
       <c r="M159">
-        <v>1.396825396825397</v>
+        <v>1.527777777777778</v>
       </c>
       <c r="N159">
-        <v>1.396825396825397</v>
+        <v>1.527777777777778</v>
       </c>
       <c r="Q159" t="s">
         <v>242</v>
@@ -9679,10 +9679,10 @@
         <v>1</v>
       </c>
       <c r="M161">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="N161">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="Q161" t="s">
         <v>242</v>
@@ -10156,10 +10156,10 @@
         <v>1</v>
       </c>
       <c r="M170">
-        <v>1.391534391534391</v>
+        <v>1.51984126984127</v>
       </c>
       <c r="N170">
-        <v>1.391534391534391</v>
+        <v>1.51984126984127</v>
       </c>
       <c r="Q170" t="s">
         <v>242</v>
@@ -10262,10 +10262,10 @@
         <v>1</v>
       </c>
       <c r="M172">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="N172">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="Q172" t="s">
         <v>242</v>
@@ -10739,10 +10739,10 @@
         <v>1</v>
       </c>
       <c r="M181">
-        <v>1.388888888888889</v>
+        <v>1.514550264550265</v>
       </c>
       <c r="N181">
-        <v>1.388888888888889</v>
+        <v>1.514550264550265</v>
       </c>
       <c r="Q181" t="s">
         <v>242</v>
@@ -10845,10 +10845,10 @@
         <v>1</v>
       </c>
       <c r="M183">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="N183">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="Q183" t="s">
         <v>242</v>
@@ -11322,10 +11322,10 @@
         <v>1</v>
       </c>
       <c r="M192">
-        <v>1.388888888888889</v>
+        <v>1.514550264550265</v>
       </c>
       <c r="N192">
-        <v>1.388888888888889</v>
+        <v>1.514550264550265</v>
       </c>
       <c r="Q192" t="s">
         <v>242</v>
@@ -11428,10 +11428,10 @@
         <v>1</v>
       </c>
       <c r="M194">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="N194">
-        <v>1.492424242424242</v>
+        <v>1.546296296296296</v>
       </c>
       <c r="Q194" t="s">
         <v>242</v>
